--- a/outputs/explain_model_coefficients.xlsx
+++ b/outputs/explain_model_coefficients.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,22 +460,22 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.08618677742681269</v>
+        <v>0.08618677742681274</v>
       </c>
       <c r="C2" t="n">
         <v>0.0002960782174701334</v>
       </c>
       <c r="D2" t="n">
-        <v>291.0946241275135</v>
+        <v>291.0946241275137</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0.08560594017272988</v>
+        <v>0.08560594017272993</v>
       </c>
       <c r="G2" t="n">
-        <v>0.0867676146808955</v>
+        <v>0.08676761468089556</v>
       </c>
     </row>
     <row r="3">
@@ -485,22 +485,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.08178827820422775</v>
+        <v>0.08178827820422779</v>
       </c>
       <c r="C3" t="n">
-        <v>0.0002960782174701338</v>
+        <v>0.0002960782174701337</v>
       </c>
       <c r="D3" t="n">
-        <v>276.238755093417</v>
+        <v>276.2387550934172</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0.08120744095014494</v>
+        <v>0.08120744095014498</v>
       </c>
       <c r="G3" t="n">
-        <v>0.08236911545831056</v>
+        <v>0.0823691154583106</v>
       </c>
     </row>
     <row r="4">
@@ -510,22 +510,22 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.06713199328490117</v>
+        <v>0.06713199328490121</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0003620132821493224</v>
+        <v>0.0003620132821493233</v>
       </c>
       <c r="D4" t="n">
-        <v>185.4406912540041</v>
+        <v>185.4406912540038</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0.06642180662361349</v>
+        <v>0.06642180662361354</v>
       </c>
       <c r="G4" t="n">
-        <v>0.06784217994618885</v>
+        <v>0.06784217994618889</v>
       </c>
     </row>
     <row r="5">
@@ -535,22 +535,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.009662857030872118</v>
+        <v>0.09662857030872125</v>
       </c>
       <c r="C5" t="n">
-        <v>3.620132821493221e-05</v>
+        <v>0.0003620132821493233</v>
       </c>
       <c r="D5" t="n">
-        <v>266.9199586684339</v>
+        <v>266.9199586684333</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0.00959183836474335</v>
+        <v>0.09591838364743357</v>
       </c>
       <c r="G5" t="n">
-        <v>0.009733875697000885</v>
+        <v>0.09733875697000893</v>
       </c>
     </row>
     <row r="6">
@@ -560,47 +560,22 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.05175402637269419</v>
+        <v>-0.05175402637269422</v>
       </c>
       <c r="C6" t="n">
-        <v>0.002627731502571953</v>
+        <v>0.002627731502571951</v>
       </c>
       <c r="D6" t="n">
-        <v>-19.69532515861637</v>
+        <v>-19.6953251586164</v>
       </c>
       <c r="E6" t="n">
-        <v>7.052729030520373e-76</v>
+        <v>7.052729030518078e-76</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.05690903022087416</v>
+        <v>-0.05690903022087418</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.04659902252451422</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Rust0_t</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>0.02898857109261635</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0.0001086039846447967</v>
-      </c>
-      <c r="D7" t="n">
-        <v>266.9199586684337</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0.02877551509423005</v>
-      </c>
-      <c r="G7" t="n">
-        <v>0.02920162709100265</v>
+        <v>-0.04659902252451426</v>
       </c>
     </row>
   </sheetData>
